--- a/datasets/day1_excel_foundations/05_functions_and_data_tips/practice_completed.xlsx
+++ b/datasets/day1_excel_foundations/05_functions_and_data_tips/practice_completed.xlsx
@@ -466,15 +466,15 @@
   <cols>
     <col width="10.5" customWidth="1" min="1" max="1"/>
     <col width="13.5" customWidth="1" min="2" max="2"/>
-    <col width="16.5" customWidth="1" min="3" max="3"/>
-    <col width="15.5" customWidth="1" min="4" max="4"/>
+    <col width="19.5" customWidth="1" min="3" max="3"/>
+    <col width="10.5" customWidth="1" min="4" max="4"/>
     <col width="22.5" customWidth="1" min="5" max="5"/>
     <col width="12.5" customWidth="1" min="6" max="6"/>
     <col width="10.5" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="42" customWidth="1" min="9" max="9"/>
     <col width="21.5" customWidth="1" min="11" max="11"/>
-    <col width="39.5" customWidth="1" min="12" max="12"/>
+    <col width="34.5" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -540,12 +540,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Chen Li</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -589,12 +589,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -638,12 +638,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -687,12 +687,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -736,12 +736,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -785,12 +785,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chen Li</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -932,12 +932,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Michael Miller</t>
+          <t>Nyasha Banda</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1011,11 +1011,11 @@
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>US Sales</t>
+          <t>Zimbabwe Sales</t>
         </is>
       </c>
       <c r="L11" s="7">
-        <f>SUMIF(D2:D31,"United States",H2:H31)</f>
+        <f>SUMIF(D2:D31,"Zimbabwe",H2:H31)</f>
         <v/>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1070,12 +1070,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Michael Miller</t>
+          <t>Nyasha Banda</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1190,12 +1190,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1230,12 +1230,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sofia Lopez</t>
+          <t>Tatenda Mpofu</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1390,12 +1390,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Maria Garcia</t>
+          <t>Rutendo Chikafu</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1470,12 +1470,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1510,12 +1510,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1550,12 +1550,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>John Smith</t>
+          <t>Farai Ncube</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1590,12 +1590,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1630,12 +1630,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1670,12 +1670,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Wei Wang</t>
+          <t>Simbarashe Mutasa</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1750,12 +1750,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Wei Wang</t>
+          <t>Simbarashe Mutasa</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
